--- a/samples/issueddevice_out/issued-device_field_mapping.xlsx
+++ b/samples/issueddevice_out/issued-device_field_mapping.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>7a531a3c678950ce</t>
+          <t>0d955901f5735fb4</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>SOR Polymorphizer 6.6</t>
+          <t>SOR Polymorphizer 6.7</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>2026-09-09T23:59:51+00:00</t>
+          <t>2026-09-10T00:27:59+00:00</t>
         </is>
       </c>
     </row>

--- a/samples/issueddevice_out/issued-device_field_mapping.xlsx
+++ b/samples/issueddevice_out/issued-device_field_mapping.xlsx
@@ -652,7 +652,7 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>0d955901f5735fb4</t>
+          <t>9c82b9975a39d7e9</t>
         </is>
       </c>
     </row>
@@ -664,7 +664,7 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>SOR Polymorphizer 6.7</t>
+          <t>SOR Polymorphizer 6.8</t>
         </is>
       </c>
     </row>
@@ -676,7 +676,7 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>2026-09-10T00:27:59+00:00</t>
+          <t>2026-09-11T05:20:35+00:00</t>
         </is>
       </c>
     </row>
